--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/dic-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/dic-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1157.21</v>
+        <v>1141.35</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1119.88</v>
+        <v>1104.53</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>15091.44</v>
+        <v>14888</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>630.53</v>
+        <v>623.76</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>567.47</v>
+        <v>561.39</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8535.68</v>
+        <v>8444.09</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15179.44</v>
+        <v>15103.88</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1803.93</v>
+        <v>1781.82</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>33515.41</v>
+        <v>33211.71</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6467.76</v>
+        <v>6491.23</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9327.65</v>
+        <v>9315.32</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8315.690000000001</v>
+        <v>8304.700000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>32690.79</v>
+        <v>32738.51</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>300954.1</v>
+        <v>303167.25</v>
       </c>
     </row>
     <row r="16">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>494472.34</v>
+        <v>500977.05</v>
       </c>
     </row>
     <row r="17">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>33557.2</v>
+        <v>33998.64</v>
       </c>
     </row>
     <row r="18">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>52006.07</v>
+        <v>52355.38</v>
       </c>
     </row>
     <row r="19">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>52006.07</v>
+        <v>52355.38</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2771.9</v>
+        <v>2790.78</v>
       </c>
     </row>
     <row r="21">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5669438.88</v>
+        <v>5708070.46</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/dic-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/dic-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/dic-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/dic-2025.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal de la SVS</t>
+          <t>COMISION PARA EL MERCADO FINANCIERO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BIENESTAR DEL CONSEJO DE DEFENSA DEL ESTADO</t>
+          <t>Consejo de Defensa del Estado</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/dic-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/dic-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1485,7 +1537,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1546,7 +1602,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1607,7 +1667,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1668,7 +1732,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
